--- a/Homework2/my-simulation/question6.xlsx
+++ b/Homework2/my-simulation/question6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619AA34F-9337-40D9-9A73-36F72FA317EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534030E1-9002-4B41-B04C-9D6C1D1A5833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E80FAFA-0C40-4CBD-8A86-3F1424DEA9C9}"/>
   </bookViews>

--- a/Homework2/my-simulation/question6.xlsx
+++ b/Homework2/my-simulation/question6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534030E1-9002-4B41-B04C-9D6C1D1A5833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD30548-6F14-4F70-A53C-7A18DA85D4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E80FAFA-0C40-4CBD-8A86-3F1424DEA9C9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>X--Trace 1::[V(vo)]</t>
   </si>
@@ -56,20 +56,46 @@
     <t>MIN Delta V</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
     <t>MAX V_o</t>
   </si>
   <si>
     <t>MIN V_o</t>
+  </si>
+  <si>
+    <t>Error_input</t>
+  </si>
+  <si>
+    <t>Error_output</t>
+  </si>
+  <si>
+    <t>Max Error Input</t>
+  </si>
+  <si>
+    <t>Min Error Output</t>
+  </si>
+  <si>
+    <t>Max Error Output</t>
+  </si>
+  <si>
+    <t>Min Error Input</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.00000%"/>
+    <numFmt numFmtId="165" formatCode="0.000000%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,14 +121,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -439,7 +469,12 @@
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -455,6 +490,12 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -471,15 +512,20 @@
         <f>B2-C2</f>
         <v>1.0671669256573146E-2</v>
       </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <f>MAX(D2:D202)</f>
-        <v>3.0654475136173254E-2</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
+      <c r="E2" s="2">
+        <f>(B2/100-A2)/A2</f>
+        <v>1.0671669256573195E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <f>(B2-C2)/C2</f>
+        <v>1.0671669256573146E-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1">
+        <f>MAX($E:$E)</f>
+        <v>1.0671669256573195E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -497,15 +543,20 @@
         <f t="shared" ref="D3:D66" si="1">B3-C3</f>
         <v>1.0771583290991149E-2</v>
       </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <f>MIN(D2:D202)</f>
-        <v>1.0671669256573146E-2</v>
-      </c>
-      <c r="H3" t="s">
-        <v>6</v>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E66" si="2">(B3/100-A3)/A3</f>
+        <v>1.0664933951476482E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F66" si="3">(B3-C3)/C3</f>
+        <v>1.0664933951476385E-2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1">
+        <f>MIN($E:$E)</f>
+        <v>1.0218158378724444E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -523,6 +574,14 @@
         <f t="shared" si="1"/>
         <v>1.0871499332058221E-2</v>
       </c>
+      <c r="E4" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0658332678488371E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0658332678488454E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -539,12 +598,20 @@
         <f t="shared" si="1"/>
         <v>1.0971412024784355E-2</v>
       </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <f>MAX($B$2:$B$202)</f>
-        <v>3.0306544751361613</v>
+      <c r="E5" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0651856334742067E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0651856334742095E-2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1">
+        <f>MAX($F:$F)</f>
+        <v>1.0671669256573146E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -562,12 +629,20 @@
         <f t="shared" si="1"/>
         <v>1.1071324717879749E-2</v>
       </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <f>MIN($B$2:$B$202)</f>
-        <v>1.0106716692565731</v>
+      <c r="E6" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0645504536422925E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0645504536422837E-2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1">
+        <f>MIN($F:$F)</f>
+        <v>1.021815837872446E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -585,6 +660,14 @@
         <f t="shared" si="1"/>
         <v>1.1171237410771973E-2</v>
       </c>
+      <c r="E7" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0639273724544806E-2</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0639273724544738E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -601,6 +684,21 @@
         <f t="shared" si="1"/>
         <v>1.1271152448113275E-2</v>
       </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0633162686899235E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="3"/>
+        <v>1.063316268689932E-2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <f>MAX(D2:D202)</f>
+        <v>3.0654475136173254E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -617,6 +715,21 @@
         <f t="shared" si="1"/>
         <v>1.1371065141092984E-2</v>
       </c>
+      <c r="E9" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0627163683264482E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0627163683264475E-2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <f>MIN(D2:D202)</f>
+        <v>1.0671669256573146E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -633,6 +746,14 @@
         <f t="shared" si="1"/>
         <v>1.1470981351488163E-2</v>
       </c>
+      <c r="E10" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0621279029155859E-2</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="3"/>
+        <v>1.062127902915571E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -649,6 +770,21 @@
         <f t="shared" si="1"/>
         <v>1.1570895216309829E-2</v>
       </c>
+      <c r="E11" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0615500198449312E-2</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0615500198449391E-2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <f>MAX($B$2:$B$202)</f>
+        <v>3.0306544751361613</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -665,6 +801,21 @@
         <f t="shared" si="1"/>
         <v>1.1670809081720135E-2</v>
       </c>
+      <c r="E12" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0609826437927376E-2</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="3"/>
+        <v>1.06098264379274E-2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <f>MIN($B$2:$B$202)</f>
+        <v>1.0106716692565731</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -681,6 +832,14 @@
         <f t="shared" si="1"/>
         <v>1.1770721774578607E-2</v>
       </c>
+      <c r="E13" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0604253850971768E-2</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0604253850971725E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -697,6 +856,14 @@
         <f t="shared" si="1"/>
         <v>1.1870637984751742E-2</v>
       </c>
+      <c r="E14" s="2">
+        <f t="shared" si="2"/>
+        <v>1.059878391495679E-2</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="3"/>
+        <v>1.059878391495692E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -713,6 +880,14 @@
         <f t="shared" si="1"/>
         <v>1.1970550677329994E-2</v>
       </c>
+      <c r="E15" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0593407679053092E-2</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0593407679053099E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -729,8 +904,16 @@
         <f t="shared" si="1"/>
         <v>1.2070466887458275E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0588128848647679E-2</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0588128848647618E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1.1499999999999991E-2</v>
       </c>
@@ -745,8 +928,16 @@
         <f t="shared" si="1"/>
         <v>1.2170378407927673E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="2">
+        <f t="shared" si="2"/>
+        <v>1.058293774602403E-2</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0582937746024073E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1.1599999999999991E-2</v>
       </c>
@@ -761,8 +952,16 @@
         <f t="shared" si="1"/>
         <v>1.2270292273391714E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0577838166717046E-2</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0577838166717004E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1.169999999999999E-2</v>
       </c>
@@ -777,8 +976,16 @@
         <f t="shared" si="1"/>
         <v>1.237020848362369E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0572827763780934E-2</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0572827763780941E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1.1799999999999989E-2</v>
       </c>
@@ -793,8 +1000,16 @@
         <f t="shared" si="1"/>
         <v>1.2470121176390236E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0567899302025533E-2</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0567899302025634E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1.1899999999999989E-2</v>
       </c>
@@ -809,8 +1024,16 @@
         <f t="shared" si="1"/>
         <v>1.2570035041485683E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0563054656710622E-2</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0563054656710669E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1.1999999999999988E-2</v>
       </c>
@@ -825,8 +1048,16 @@
         <f t="shared" si="1"/>
         <v>1.2669948906877337E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="2">
+        <f t="shared" si="2"/>
+        <v>1.05582907557312E-2</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0558290755731125E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1.2099999999999988E-2</v>
       </c>
@@ -841,8 +1072,16 @@
         <f t="shared" si="1"/>
         <v>1.2769865116635692E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0553607534409737E-2</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0553607534409672E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1.2199999999999987E-2</v>
       </c>
@@ -857,8 +1096,16 @@
         <f t="shared" si="1"/>
         <v>1.2869776637098873E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0548997243523621E-2</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0548997243523678E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1.2299999999999986E-2</v>
       </c>
@@ -873,8 +1120,16 @@
         <f t="shared" si="1"/>
         <v>1.2969691675236428E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0544464776615078E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0544464776614993E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1.2399999999999986E-2</v>
       </c>
@@ -889,8 +1144,16 @@
         <f t="shared" si="1"/>
         <v>1.3069604367629717E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0540003522282132E-2</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0540003522282041E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1.2499999999999985E-2</v>
       </c>
@@ -905,8 +1168,16 @@
         <f t="shared" si="1"/>
         <v>1.3169519405583641E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0535615524466814E-2</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0535615524466926E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1.2599999999999984E-2</v>
       </c>
@@ -921,8 +1192,16 @@
         <f t="shared" si="1"/>
         <v>1.3269433270912012E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0531296246755556E-2</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0531296246755579E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1.2699999999999984E-2</v>
       </c>
@@ -937,8 +1216,16 @@
         <f t="shared" si="1"/>
         <v>1.3369348308169604E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0527045911944649E-2</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0527045911944583E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1.2799999999999983E-2</v>
       </c>
@@ -953,8 +1240,16 @@
         <f t="shared" si="1"/>
         <v>1.3469261001220367E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0522860157203349E-2</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0522860157203426E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1.2899999999999983E-2</v>
       </c>
@@ -969,8 +1264,16 @@
         <f t="shared" si="1"/>
         <v>1.3569174866484346E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0518740206577065E-2</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0518740206577027E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1.2999999999999982E-2</v>
       </c>
@@ -985,8 +1288,16 @@
         <f t="shared" si="1"/>
         <v>1.3669089904330356E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0514684541792585E-2</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0514684541792595E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1.3099999999999981E-2</v>
       </c>
@@ -1001,8 +1312,16 @@
         <f t="shared" si="1"/>
         <v>1.3769002596733193E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0510689005139847E-2</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0510689005139857E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1.3199999999999981E-2</v>
       </c>
@@ -1017,8 +1336,16 @@
         <f t="shared" si="1"/>
         <v>1.3868918807079078E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0506756672029615E-2</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="3"/>
+        <v>1.050675667202962E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1.329999999999998E-2</v>
       </c>
@@ -1033,8 +1360,16 @@
         <f t="shared" si="1"/>
         <v>1.3968831499974854E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0502880827048824E-2</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0502880827048778E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1.339999999999998E-2</v>
       </c>
@@ -1049,8 +1384,16 @@
         <f t="shared" si="1"/>
         <v>1.4068746537806875E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0499064580452862E-2</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0499064580452909E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1.3499999999999979E-2</v>
       </c>
@@ -1065,8 +1408,16 @@
         <f t="shared" si="1"/>
         <v>1.4168660403235833E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0495304002396857E-2</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="3"/>
+        <v>1.049530400239693E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1.3599999999999978E-2</v>
       </c>
@@ -1081,8 +1432,16 @@
         <f t="shared" si="1"/>
         <v>1.4268575440465447E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0491599588577597E-2</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0491599588577552E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1.3699999999999978E-2</v>
       </c>
@@ -1097,8 +1456,16 @@
         <f t="shared" si="1"/>
         <v>1.4368489306092469E-2</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="2">
+        <f t="shared" si="2"/>
+        <v>1.048794839860771E-2</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0487948398607658E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1.3799999999999977E-2</v>
       </c>
@@ -1113,8 +1480,16 @@
         <f t="shared" si="1"/>
         <v>1.446840434357699E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0484350973606517E-2</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0484350973606532E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1.3899999999999977E-2</v>
       </c>
@@ -1129,8 +1504,16 @@
         <f t="shared" si="1"/>
         <v>1.4568315864062598E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0480802779901138E-2</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0480802779901167E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1.3999999999999976E-2</v>
       </c>
@@ -1145,8 +1528,16 @@
         <f t="shared" si="1"/>
         <v>1.4668232074296572E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0477308624497684E-2</v>
+      </c>
+      <c r="F42" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0477308624497569E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1.4099999999999975E-2</v>
       </c>
@@ -1161,8 +1552,16 @@
         <f t="shared" si="1"/>
         <v>1.4768143594469763E-2</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0473860705297693E-2</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0473860705297723E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1.4199999999999975E-2</v>
       </c>
@@ -1177,8 +1576,16 @@
         <f t="shared" si="1"/>
         <v>1.4868057459703099E-2</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0470462999790963E-2</v>
+      </c>
+      <c r="F44" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0470462999790934E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1.4299999999999974E-2</v>
       </c>
@@ -1193,8 +1600,16 @@
         <f t="shared" si="1"/>
         <v>1.4967971324786555E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="2">
+        <f t="shared" si="2"/>
+        <v>1.046711281453616E-2</v>
+      </c>
+      <c r="F45" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0467112814536071E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1.4399999999999974E-2</v>
       </c>
@@ -1209,8 +1624,16 @@
         <f t="shared" si="1"/>
         <v>1.5067886362662986E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0463809974071536E-2</v>
+      </c>
+      <c r="F46" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0463809974071538E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1.4499999999999973E-2</v>
       </c>
@@ -1225,8 +1648,16 @@
         <f t="shared" si="1"/>
         <v>1.5167800227955608E-2</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0460551881348682E-2</v>
+      </c>
+      <c r="F47" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0460551881348715E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1.4599999999999972E-2</v>
       </c>
@@ -1241,8 +1672,16 @@
         <f t="shared" si="1"/>
         <v>1.5267712920774557E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0457337616968895E-2</v>
+      </c>
+      <c r="F48" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0457337616968893E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1.4699999999999972E-2</v>
       </c>
@@ -1257,8 +1696,16 @@
         <f t="shared" si="1"/>
         <v>1.5367629130989435E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0454169476863492E-2</v>
+      </c>
+      <c r="F49" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0454169476863583E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1.4799999999999971E-2</v>
       </c>
@@ -1273,8 +1720,16 @@
         <f t="shared" si="1"/>
         <v>1.5467542996033368E-2</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0451042564887379E-2</v>
+      </c>
+      <c r="F50" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0451042564887431E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1.4899999999999971E-2</v>
       </c>
@@ -1289,8 +1744,16 @@
         <f t="shared" si="1"/>
         <v>1.5567456861169227E-2</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0447957624945806E-2</v>
+      </c>
+      <c r="F51" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0447957624945809E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1.499999999999997E-2</v>
       </c>
@@ -1305,8 +1768,16 @@
         <f t="shared" si="1"/>
         <v>1.566736955397352E-2</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0444913035982335E-2</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0444913035982368E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1.5099999999999969E-2</v>
       </c>
@@ -1321,8 +1792,16 @@
         <f t="shared" si="1"/>
         <v>1.5767284591709396E-2</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="2">
+        <f t="shared" si="2"/>
+        <v>1.044191032563541E-2</v>
+      </c>
+      <c r="F53" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0441910325635384E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1.5199999999999969E-2</v>
       </c>
@@ -1337,8 +1816,16 @@
         <f t="shared" si="1"/>
         <v>1.5867197284594514E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0438945581970106E-2</v>
+      </c>
+      <c r="F54" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0438945581970097E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1.5299999999999968E-2</v>
       </c>
@@ -1353,8 +1840,16 @@
         <f t="shared" si="1"/>
         <v>1.5967113494703922E-2</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0436021891963406E-2</v>
+      </c>
+      <c r="F55" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0436021891963368E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1.5399999999999968E-2</v>
       </c>
@@ -1369,8 +1864,16 @@
         <f t="shared" si="1"/>
         <v>1.6067026187507105E-2</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0433133887991591E-2</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="3"/>
+        <v>1.043313388799165E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1.5499999999999967E-2</v>
       </c>
@@ -1385,8 +1888,16 @@
         <f t="shared" si="1"/>
         <v>1.6166940052915191E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0430283905106663E-2</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0430283905106598E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1.5599999999999966E-2</v>
       </c>
@@ -1401,8 +1912,16 @@
         <f t="shared" si="1"/>
         <v>1.6266856262900919E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0427471963398025E-2</v>
+      </c>
+      <c r="F58" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0427471963398048E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1.5699999999999967E-2</v>
       </c>
@@ -1417,8 +1936,16 @@
         <f t="shared" si="1"/>
         <v>1.6366767783423608E-2</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0424692855683839E-2</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0424692855683848E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1.5799999999999967E-2</v>
       </c>
@@ -1433,8 +1960,16 @@
         <f t="shared" si="1"/>
         <v>1.6466683993452635E-2</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0421951894590244E-2</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0421951894590296E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.5899999999999966E-2</v>
       </c>
@@ -1449,8 +1984,16 @@
         <f t="shared" si="1"/>
         <v>1.6566595514202476E-2</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0419242461762498E-2</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0419242461762587E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1.5999999999999966E-2</v>
       </c>
@@ -1465,8 +2008,16 @@
         <f t="shared" si="1"/>
         <v>1.6666510551929248E-2</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0416569094955716E-2</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0416569094955802E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1.6099999999999965E-2</v>
       </c>
@@ -1481,8 +2032,16 @@
         <f t="shared" si="1"/>
         <v>1.6766425589495704E-2</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0413928937574925E-2</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0413928937574994E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1.6199999999999964E-2</v>
       </c>
@@ -1497,8 +2056,16 @@
         <f t="shared" si="1"/>
         <v>1.686633828215367E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0411319927255443E-2</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0411319927255374E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1.6299999999999964E-2</v>
       </c>
@@ -1513,8 +2080,16 @@
         <f t="shared" si="1"/>
         <v>1.6966252147409655E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0408743648717663E-2</v>
+      </c>
+      <c r="F65" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0408743648717604E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1.6399999999999963E-2</v>
       </c>
@@ -1529,8 +2104,16 @@
         <f t="shared" si="1"/>
         <v>1.7066166012707162E-2</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0406198788236216E-2</v>
+      </c>
+      <c r="F66" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0406198788236098E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1.6499999999999963E-2</v>
       </c>
@@ -1538,15 +2121,23 @@
         <v>1.667166078705643</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C130" si="2">A67*100</f>
+        <f t="shared" ref="C67:C130" si="4">A67*100</f>
         <v>1.6499999999999964</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D130" si="3">B67-C67</f>
+        <f t="shared" ref="D67:D130" si="5">B67-C67</f>
         <v>1.7166078705646681E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="2">
+        <f t="shared" ref="E67:E130" si="6">(B67/100-A67)/A67</f>
+        <v>1.0403684064028458E-2</v>
+      </c>
+      <c r="F67" s="2">
+        <f t="shared" ref="F67:F130" si="7">(B67-C67)/C67</f>
+        <v>1.0403684064028315E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1.6599999999999962E-2</v>
       </c>
@@ -1554,15 +2145,23 @@
         <v>1.6772659949153623</v>
       </c>
       <c r="C68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6599999999999961</v>
       </c>
       <c r="D68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7265994915366178E-2</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0401201756244635E-2</v>
+      </c>
+      <c r="F68" s="2">
+        <f t="shared" si="7"/>
+        <v>1.040120175624471E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1.6699999999999961E-2</v>
       </c>
@@ -1570,15 +2169,23 @@
         <v>1.6873659099533642</v>
       </c>
       <c r="C69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6699999999999962</v>
       </c>
       <c r="D69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7365909953368064E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0398748475070654E-2</v>
+      </c>
+      <c r="F69" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0398748475070722E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1.6799999999999961E-2</v>
       </c>
@@ -1586,15 +2193,23 @@
         <v>1.6974658238185816</v>
       </c>
       <c r="C70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6799999999999962</v>
       </c>
       <c r="D70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7465823818585413E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0396323701538961E-2</v>
+      </c>
+      <c r="F70" s="2">
+        <f t="shared" si="7"/>
+        <v>1.039632370153896E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1.689999999999996E-2</v>
       </c>
@@ -1602,15 +2217,23 @@
         <v>1.7075657376839719</v>
       </c>
       <c r="C71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6899999999999959</v>
       </c>
       <c r="D71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7565737683975957E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0393927623654462E-2</v>
+      </c>
+      <c r="F71" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0393927623654438E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1.699999999999996E-2</v>
       </c>
@@ -1618,15 +2241,23 @@
         <v>1.7176656527212883</v>
       </c>
       <c r="C72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.699999999999996</v>
       </c>
       <c r="D72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7665652721292391E-2</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0391560424289634E-2</v>
+      </c>
+      <c r="F72" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0391560424289667E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1.7099999999999959E-2</v>
       </c>
@@ -1634,15 +2265,23 @@
         <v>1.7277655665864038</v>
       </c>
       <c r="C73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.709999999999996</v>
       </c>
       <c r="D73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7765566586407822E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0389220225969494E-2</v>
+      </c>
+      <c r="F73" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0389220225969512E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1.7199999999999958E-2</v>
       </c>
@@ -1650,15 +2289,23 @@
         <v>1.7378654792796293</v>
       </c>
       <c r="C74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7199999999999958</v>
       </c>
       <c r="D74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7865479279633556E-2</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0386906557926527E-2</v>
+      </c>
+      <c r="F74" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0386906557926512E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1.7299999999999958E-2</v>
       </c>
@@ -1666,15 +2313,23 @@
         <v>1.7479653943173383</v>
       </c>
       <c r="C75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7299999999999958</v>
       </c>
       <c r="D75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7965394317342565E-2</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0384620992683644E-2</v>
+      </c>
+      <c r="F75" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0384620992683589E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1.7399999999999957E-2</v>
       </c>
@@ -1682,15 +2337,23 @@
         <v>1.7580653093550882</v>
       </c>
       <c r="C76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7399999999999958</v>
       </c>
       <c r="D76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8065309355092429E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0382361698328952E-2</v>
+      </c>
+      <c r="F76" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0382361698329007E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1.7499999999999957E-2</v>
       </c>
@@ -1698,15 +2361,23 @@
         <v>1.7681652220477084</v>
       </c>
       <c r="C77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7499999999999956</v>
       </c>
       <c r="D77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.816522204771287E-2</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0380126884407285E-2</v>
+      </c>
+      <c r="F77" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0380126884407381E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1.7599999999999956E-2</v>
       </c>
@@ -1714,15 +2385,23 @@
         <v>1.7782651347407972</v>
       </c>
       <c r="C78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7599999999999956</v>
       </c>
       <c r="D78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8265134740801603E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0377917466364486E-2</v>
+      </c>
+      <c r="F78" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0377917466364574E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1.7699999999999955E-2</v>
       </c>
@@ -1730,15 +2409,23 @@
         <v>1.7883650486059535</v>
       </c>
       <c r="C79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7699999999999956</v>
       </c>
       <c r="D79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.836504860595789E-2</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0375733675682427E-2</v>
+      </c>
+      <c r="F79" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0375733675682449E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1.7799999999999955E-2</v>
       </c>
@@ -1746,15 +2433,23 @@
         <v>1.7984649624710949</v>
       </c>
       <c r="C80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7799999999999954</v>
       </c>
       <c r="D80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8464962471099522E-2</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0373574421965941E-2</v>
+      </c>
+      <c r="F80" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0373574421966051E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1.7899999999999954E-2</v>
       </c>
@@ -1762,15 +2457,23 @@
         <v>1.8085648775086693</v>
       </c>
       <c r="C81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7899999999999954</v>
       </c>
       <c r="D81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8564877508673971E-2</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0371439948979799E-2</v>
+      </c>
+      <c r="F81" s="2">
+        <f t="shared" si="7"/>
+        <v>1.03714399489799E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1.7999999999999954E-2</v>
       </c>
@@ -1778,15 +2481,23 @@
         <v>1.8186647925462562</v>
       </c>
       <c r="C82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7999999999999954</v>
       </c>
       <c r="D82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8664792546260855E-2</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0369329192367107E-2</v>
+      </c>
+      <c r="F82" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0369329192367169E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1.8099999999999953E-2</v>
       </c>
@@ -1794,15 +2505,23 @@
         <v>1.8287647052393647</v>
       </c>
       <c r="C83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8099999999999954</v>
       </c>
       <c r="D83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.876470523936935E-2</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0367240463740145E-2</v>
+      </c>
+      <c r="F83" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0367240463739999E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1.8199999999999952E-2</v>
       </c>
@@ -1810,15 +2529,23 @@
         <v>1.8388646191047189</v>
       </c>
       <c r="C84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8199999999999952</v>
       </c>
       <c r="D84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8864619104723701E-2</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0365175332265835E-2</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0365175332265797E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1.8299999999999952E-2</v>
       </c>
@@ -1826,15 +2553,23 @@
         <v>1.8489645329697979</v>
       </c>
       <c r="C85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8299999999999952</v>
       </c>
       <c r="D85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8964532969802717E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0363132770384071E-2</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0363132770384025E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1.8399999999999951E-2</v>
       </c>
@@ -1842,15 +2577,23 @@
         <v>1.8590644480075067</v>
       </c>
       <c r="C86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8399999999999952</v>
       </c>
       <c r="D86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9064448007511503E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0361113047560643E-2</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0361113047560627E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1.8499999999999951E-2</v>
       </c>
@@ -1858,15 +2601,23 @@
         <v>1.8691643618727654</v>
       </c>
       <c r="C87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.849999999999995</v>
       </c>
       <c r="D87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9164361872770375E-2</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="2">
+        <f t="shared" si="6"/>
+        <v>1.03591145258218E-2</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0359114525821852E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1.859999999999995E-2</v>
       </c>
@@ -1874,15 +2625,23 @@
         <v>1.8792642769103516</v>
       </c>
       <c r="C88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.859999999999995</v>
       </c>
       <c r="D88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9264276910356593E-2</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0357138123847628E-2</v>
+      </c>
+      <c r="F88" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0357138123847658E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1.8699999999999949E-2</v>
       </c>
@@ -1890,15 +2649,23 @@
         <v>1.8893641896032545</v>
       </c>
       <c r="C89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.869999999999995</v>
       </c>
       <c r="D89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9364189603259474E-2</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0355181606021242E-2</v>
+      </c>
+      <c r="F89" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0355181606021138E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1.8799999999999949E-2</v>
       </c>
@@ -1906,15 +2673,23 @@
         <v>1.8994641034684834</v>
       </c>
       <c r="C90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8799999999999948</v>
       </c>
       <c r="D90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9464103468488592E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0353246525791825E-2</v>
+      </c>
+      <c r="F90" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0353246525791832E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1.8899999999999948E-2</v>
       </c>
@@ -1922,15 +2697,23 @@
         <v>1.9095640196787167</v>
       </c>
       <c r="C91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8899999999999948</v>
       </c>
       <c r="D91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.95640196787219E-2</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0351333163344942E-2</v>
+      </c>
+      <c r="F91" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0351333163344949E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1.8999999999999947E-2</v>
       </c>
@@ -1938,15 +2721,23 @@
         <v>1.9196639335436132</v>
       </c>
       <c r="C92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8999999999999948</v>
       </c>
       <c r="D92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9663933543618395E-2</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0349438707167619E-2</v>
+      </c>
+      <c r="F92" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0349438707167605E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1.9099999999999947E-2</v>
       </c>
@@ -1954,15 +2745,23 @@
         <v>1.9297638450641939</v>
       </c>
       <c r="C93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9099999999999946</v>
       </c>
       <c r="D93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9763845064199259E-2</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="2">
+        <f t="shared" si="6"/>
+        <v>1.034756286083733E-2</v>
+      </c>
+      <c r="F93" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0347562860837338E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1.9199999999999946E-2</v>
       </c>
@@ -1970,15 +2769,23 @@
         <v>1.939863762446683</v>
       </c>
       <c r="C94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9199999999999946</v>
       </c>
       <c r="D94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9863762446688416E-2</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0345709607650159E-2</v>
+      </c>
+      <c r="F94" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0345709607650246E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1.9299999999999946E-2</v>
       </c>
@@ -1986,15 +2793,23 @@
         <v>1.9499636739673074</v>
       </c>
       <c r="C95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9299999999999946</v>
       </c>
       <c r="D95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9963673967312801E-2</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0343872521923753E-2</v>
+      </c>
+      <c r="F95" s="2">
+        <f t="shared" si="7"/>
+        <v>1.034387252192376E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1.9399999999999945E-2</v>
       </c>
@@ -2002,15 +2817,23 @@
         <v>1.960063586660211</v>
       </c>
       <c r="C96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9399999999999946</v>
       </c>
       <c r="D96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0063586660216348E-2</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0342054979493129E-2</v>
+      </c>
+      <c r="F96" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0342054979492992E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1.9499999999999944E-2</v>
       </c>
@@ -2018,15 +2841,23 @@
         <v>1.9701635028702853</v>
       </c>
       <c r="C97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9499999999999944</v>
       </c>
       <c r="D97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0163502870290895E-2</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0340257882200552E-2</v>
+      </c>
+      <c r="F97" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0340257882200488E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1.9599999999999944E-2</v>
       </c>
@@ -2034,15 +2865,23 @@
         <v>1.9802634143904989</v>
       </c>
       <c r="C98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9599999999999944</v>
       </c>
       <c r="D98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0263414390504497E-2</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0338476729849227E-2</v>
+      </c>
+      <c r="F98" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0338476729849264E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1.9699999999999943E-2</v>
       </c>
@@ -2050,15 +2889,23 @@
         <v>1.990363329428344</v>
       </c>
       <c r="C99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9699999999999944</v>
       </c>
       <c r="D99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0363329428349619E-2</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="2">
+        <f t="shared" si="6"/>
+        <v>1.03367154458629E-2</v>
+      </c>
+      <c r="F99" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0336715445862781E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1.9799999999999943E-2</v>
       </c>
@@ -2066,15 +2913,23 @@
         <v>2.0004632421209405</v>
       </c>
       <c r="C100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9799999999999942</v>
       </c>
       <c r="D100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0463242120946301E-2</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0334970768154721E-2</v>
+      </c>
+      <c r="F100" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0334970768154728E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1.9899999999999942E-2</v>
       </c>
@@ -2082,15 +2937,23 @@
         <v>2.0105631583313341</v>
       </c>
       <c r="C101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9899999999999942</v>
       </c>
       <c r="D101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0563158331339926E-2</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0333245392633137E-2</v>
+      </c>
+      <c r="F101" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0333245392633158E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1.9999999999999941E-2</v>
       </c>
@@ -2098,15 +2961,23 @@
         <v>2.0206630721964225</v>
       </c>
       <c r="C102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999942</v>
       </c>
       <c r="D102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0663072196428267E-2</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" s="2">
+        <f t="shared" si="6"/>
+        <v>1.033153609821417E-2</v>
+      </c>
+      <c r="F102" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0331536098214163E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2.0099999999999941E-2</v>
       </c>
@@ -2114,15 +2985,23 @@
         <v>2.0307629848894195</v>
       </c>
       <c r="C103">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.009999999999994</v>
       </c>
       <c r="D103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0762984889425518E-2</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0329843228569897E-2</v>
+      </c>
+      <c r="F103" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0329843228569941E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2.019999999999994E-2</v>
       </c>
@@ -2130,15 +3009,23 @@
         <v>2.0408628999269993</v>
       </c>
       <c r="C104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0199999999999942</v>
       </c>
       <c r="D104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0862899927005074E-2</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E104" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0328168280695797E-2</v>
+      </c>
+      <c r="F104" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0328168280695611E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2.029999999999994E-2</v>
       </c>
@@ -2146,15 +3033,23 @@
         <v>2.0509628149645738</v>
       </c>
       <c r="C105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.029999999999994</v>
       </c>
       <c r="D105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0962814964579746E-2</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E105" s="2">
+        <f t="shared" si="6"/>
+        <v>1.032650983476846E-2</v>
+      </c>
+      <c r="F105" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0326509834768379E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2.0399999999999939E-2</v>
       </c>
@@ -2162,15 +3057,23 @@
         <v>2.061062727657804</v>
       </c>
       <c r="C106">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0399999999999938</v>
       </c>
       <c r="D106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1062727657810143E-2</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0324866498926605E-2</v>
+      </c>
+      <c r="F106" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0324866498926572E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2.0499999999999938E-2</v>
       </c>
@@ -2178,15 +3081,23 @@
         <v>2.0711626438677904</v>
       </c>
       <c r="C107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.049999999999994</v>
       </c>
       <c r="D107">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1162643867796316E-2</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0323240911120274E-2</v>
+      </c>
+      <c r="F107" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0323240911120184E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2.0599999999999938E-2</v>
       </c>
@@ -2194,15 +3105,23 @@
         <v>2.0812625577327908</v>
       </c>
       <c r="C108">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0599999999999938</v>
       </c>
       <c r="D108">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1262557732796949E-2</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0321629967377273E-2</v>
+      </c>
+      <c r="F108" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0321629967377191E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2.0699999999999937E-2</v>
       </c>
@@ -2210,15 +3129,23 @@
         <v>2.0913624715978196</v>
       </c>
       <c r="C109">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0699999999999936</v>
       </c>
       <c r="D109">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1362471597826005E-2</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0320034588321692E-2</v>
+      </c>
+      <c r="F109" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0320034588321774E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2.0799999999999937E-2</v>
       </c>
@@ -2226,15 +3153,23 @@
         <v>2.10146238429112</v>
       </c>
       <c r="C110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0799999999999939</v>
       </c>
       <c r="D110">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1462384291126124E-2</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0318453986118407E-2</v>
+      </c>
+      <c r="F110" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0318453986118359E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2.0899999999999936E-2</v>
       </c>
@@ -2242,15 +3177,23 @@
         <v>2.1115622993286522</v>
       </c>
       <c r="C111">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0899999999999936</v>
       </c>
       <c r="D111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1562299328658607E-2</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E111" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0316889630937211E-2</v>
+      </c>
+      <c r="F111" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0316889630937165E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2.0999999999999935E-2</v>
       </c>
@@ -2258,15 +3201,23 @@
         <v>2.121662213194015</v>
       </c>
       <c r="C112">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0999999999999934</v>
       </c>
       <c r="D112">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1662213194021618E-2</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0315339616200762E-2</v>
+      </c>
+      <c r="F112" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0315339616200802E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2.1099999999999935E-2</v>
       </c>
@@ -2274,15 +3225,23 @@
         <v>2.1317621270591407</v>
       </c>
       <c r="C113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1099999999999937</v>
       </c>
       <c r="D113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1762127059147041E-2</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E113" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0313804293434654E-2</v>
+      </c>
+      <c r="F113" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0313804293434647E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2.1199999999999934E-2</v>
       </c>
@@ -2290,15 +3249,23 @@
         <v>2.1418620409245195</v>
       </c>
       <c r="C114">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1199999999999934</v>
       </c>
       <c r="D114">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1862040924526038E-2</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0312283454965217E-2</v>
+      </c>
+      <c r="F114" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0312283454965144E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2.1299999999999934E-2</v>
       </c>
@@ -2306,15 +3273,23 @@
         <v>2.1519619547895816</v>
       </c>
       <c r="C115">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1299999999999932</v>
       </c>
       <c r="D115">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.19619547895884E-2</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E115" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0310776896520324E-2</v>
+      </c>
+      <c r="F115" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0310776896520409E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2.1399999999999933E-2</v>
       </c>
@@ -2322,15 +3297,23 @@
         <v>2.1620618686548867</v>
       </c>
       <c r="C116">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1399999999999935</v>
       </c>
       <c r="D116">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2061868654893235E-2</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0309284418174545E-2</v>
+      </c>
+      <c r="F116" s="2">
+        <f t="shared" si="7"/>
+        <v>1.030928441817444E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2.1499999999999932E-2</v>
       </c>
@@ -2338,15 +3321,23 @@
         <v>2.1721617825200554</v>
       </c>
       <c r="C117">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1499999999999932</v>
       </c>
       <c r="D117">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2161782520062179E-2</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0307805823284845E-2</v>
+      </c>
+      <c r="F117" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0307805823284766E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2.1599999999999932E-2</v>
       </c>
@@ -2354,15 +3345,23 @@
         <v>2.1822616963853232</v>
       </c>
       <c r="C118">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.159999999999993</v>
       </c>
       <c r="D118">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2261696385330154E-2</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E118" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0306340919134344E-2</v>
+      </c>
+      <c r="F118" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0306340919134363E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2.1699999999999931E-2</v>
       </c>
@@ -2370,15 +3369,23 @@
         <v>2.1923616102509258</v>
       </c>
       <c r="C119">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1699999999999933</v>
       </c>
       <c r="D119">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2361610250932529E-2</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0304889516558871E-2</v>
+      </c>
+      <c r="F119" s="2">
+        <f t="shared" si="7"/>
+        <v>1.03048895165588E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2.1799999999999931E-2</v>
       </c>
@@ -2386,15 +3393,23 @@
         <v>2.2024615252884865</v>
       </c>
       <c r="C120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1799999999999931</v>
       </c>
       <c r="D120">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2461525288493434E-2</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0303451967198779E-2</v>
+      </c>
+      <c r="F120" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0303451967198856E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2.189999999999993E-2</v>
       </c>
@@ -2402,15 +3417,23 @@
         <v>2.2125614391536472</v>
       </c>
       <c r="C121">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1899999999999928</v>
       </c>
       <c r="D121">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2561439153654383E-2</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E121" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0302027010801027E-2</v>
+      </c>
+      <c r="F121" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0302027010801122E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2.1999999999999929E-2</v>
       </c>
@@ -2418,15 +3441,23 @@
         <v>2.2226613530187134</v>
       </c>
       <c r="C122">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1999999999999931</v>
       </c>
       <c r="D122">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2661353018720298E-2</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0300615008509291E-2</v>
+      </c>
+      <c r="F122" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0300615008509258E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2.2099999999999929E-2</v>
       </c>
@@ -2434,15 +3465,23 @@
         <v>2.2327612668842387</v>
       </c>
       <c r="C123">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2099999999999929</v>
       </c>
       <c r="D123">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2761266884245845E-2</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E123" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0299215784726692E-2</v>
+      </c>
+      <c r="F123" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0299215784726661E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2.2199999999999928E-2</v>
       </c>
@@ -2450,15 +3489,23 @@
         <v>2.242861180749594</v>
       </c>
       <c r="C124">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2199999999999926</v>
       </c>
       <c r="D124">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2861180749601306E-2</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E124" s="2">
+        <f t="shared" si="6"/>
+        <v>1.029782916648702E-2</v>
+      </c>
+      <c r="F124" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0297829166487108E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2.2299999999999928E-2</v>
       </c>
@@ -2466,15 +3513,23 @@
         <v>2.2529610946145215</v>
       </c>
       <c r="C125">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2299999999999929</v>
       </c>
       <c r="D125">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.2961094614528665E-2</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E125" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0296454984093699E-2</v>
+      </c>
+      <c r="F125" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0296454984093605E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2.2399999999999927E-2</v>
       </c>
@@ -2482,15 +3537,23 @@
         <v>2.2630610096524997</v>
       </c>
       <c r="C126">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2399999999999927</v>
       </c>
       <c r="D126">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.3061009652507014E-2</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E126" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0295093594869156E-2</v>
+      </c>
+      <c r="F126" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0295093594869237E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2.2499999999999926E-2</v>
       </c>
@@ -2498,15 +3561,23 @@
         <v>2.2731609235176076</v>
       </c>
       <c r="C127">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2499999999999925</v>
       </c>
       <c r="D127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.3160923517615117E-2</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E127" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0293743785606704E-2</v>
+      </c>
+      <c r="F127" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0293743785606753E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2.2599999999999926E-2</v>
       </c>
@@ -2514,15 +3585,23 @@
         <v>2.283260837382902</v>
       </c>
       <c r="C128">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2599999999999927</v>
       </c>
       <c r="D128">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.3260837382909294E-2</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E128" s="2">
+        <f t="shared" si="6"/>
+        <v>1.02924059216414E-2</v>
+      </c>
+      <c r="F128" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0292405921641315E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2.2699999999999925E-2</v>
       </c>
@@ -2530,15 +3609,23 @@
         <v>2.2933607524207562</v>
       </c>
       <c r="C129">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2699999999999925</v>
       </c>
       <c r="D129">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.3360752420763742E-2</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E129" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0291080361569897E-2</v>
+      </c>
+      <c r="F129" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0291080361569964E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2.2799999999999924E-2</v>
       </c>
@@ -2546,15 +3633,23 @@
         <v>2.3034606651134544</v>
       </c>
       <c r="C130">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2799999999999923</v>
       </c>
       <c r="D130">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.346066511346212E-2</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E130" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0289765400641273E-2</v>
+      </c>
+      <c r="F130" s="2">
+        <f t="shared" si="7"/>
+        <v>1.0289765400641316E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2.2899999999999924E-2</v>
       </c>
@@ -2562,15 +3657,23 @@
         <v>2.3135605789788896</v>
       </c>
       <c r="C131">
-        <f t="shared" ref="C131:C194" si="4">A131*100</f>
+        <f t="shared" ref="C131:C194" si="8">A131*100</f>
         <v>2.2899999999999925</v>
       </c>
       <c r="D131">
-        <f t="shared" ref="D131:D194" si="5">B131-C131</f>
+        <f t="shared" ref="D131:D194" si="9">B131-C131</f>
         <v>2.3560578978897073E-2</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E131" s="2">
+        <f t="shared" ref="E131:E194" si="10">(B131/100-A131)/A131</f>
+        <v>1.0288462436199606E-2</v>
+      </c>
+      <c r="F131" s="2">
+        <f t="shared" ref="F131:F194" si="11">(B131-C131)/C131</f>
+        <v>1.0288462436199628E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2.2999999999999923E-2</v>
       </c>
@@ -2578,15 +3681,23 @@
         <v>2.3236604928439899</v>
       </c>
       <c r="C132">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.2999999999999923</v>
       </c>
       <c r="D132">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.3660492843997627E-2</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E132" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0287170801738103E-2</v>
+      </c>
+      <c r="F132" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0287170801738132E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2.3099999999999923E-2</v>
       </c>
@@ -2594,15 +3705,23 @@
         <v>2.3337604067092927</v>
       </c>
       <c r="C133">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3099999999999921</v>
       </c>
       <c r="D133">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.3760406709300685E-2</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E133" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0285890350346513E-2</v>
+      </c>
+      <c r="F133" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0285890350346652E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2.3199999999999922E-2</v>
       </c>
@@ -2610,15 +3729,23 @@
         <v>2.3438603217469565</v>
       </c>
       <c r="C134">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3199999999999923</v>
       </c>
       <c r="D134">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.3860321746964175E-2</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E134" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0284621442657078E-2</v>
+      </c>
+      <c r="F134" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0284621442657006E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2.3299999999999921E-2</v>
       </c>
@@ -2626,15 +3753,23 @@
         <v>2.3539602344395214</v>
       </c>
       <c r="C135">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3299999999999921</v>
       </c>
       <c r="D135">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.3960234439529327E-2</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E135" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0283362420398833E-2</v>
+      </c>
+      <c r="F135" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0283362420398888E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2.3399999999999921E-2</v>
       </c>
@@ -2642,15 +3777,23 @@
         <v>2.36406014947725</v>
       </c>
       <c r="C136">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3399999999999919</v>
       </c>
       <c r="D136">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4060149477258097E-2</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E136" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0282115161221277E-2</v>
+      </c>
+      <c r="F136" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0282115161221446E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2.349999999999992E-2</v>
       </c>
@@ -2658,15 +3801,23 @@
         <v>2.3741600621705854</v>
       </c>
       <c r="C137">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3499999999999921</v>
       </c>
       <c r="D137">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4160062170593299E-2</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E137" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0280877519401516E-2</v>
+      </c>
+      <c r="F137" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0280877519401439E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2.359999999999992E-2</v>
       </c>
@@ -2674,15 +3825,23 @@
         <v>2.3842599748634092</v>
       </c>
       <c r="C138">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3599999999999919</v>
       </c>
       <c r="D138">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4259974863417355E-2</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E138" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0279650365854764E-2</v>
+      </c>
+      <c r="F138" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0279650365854848E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2.3699999999999919E-2</v>
       </c>
@@ -2690,15 +3849,23 @@
         <v>2.394359891072952</v>
       </c>
       <c r="C139">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3699999999999921</v>
       </c>
       <c r="D139">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4359891072959883E-2</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E139" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0278435051881913E-2</v>
+      </c>
+      <c r="F139" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0278435051881842E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2.3799999999999918E-2</v>
       </c>
@@ -2706,15 +3873,23 @@
         <v>2.4044598061106974</v>
       </c>
       <c r="C140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3799999999999919</v>
       </c>
       <c r="D140">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4459806110705529E-2</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E140" s="2">
+        <f t="shared" si="10"/>
+        <v>1.027722945827968E-2</v>
+      </c>
+      <c r="F140" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0277229458279668E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2.3899999999999918E-2</v>
       </c>
@@ -2722,15 +3897,23 @@
         <v>2.4145597199761601</v>
       </c>
       <c r="C141">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3899999999999917</v>
       </c>
       <c r="D141">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4559719976168459E-2</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E141" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0276033462831962E-2</v>
+      </c>
+      <c r="F141" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0276033462832027E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2.3999999999999917E-2</v>
       </c>
@@ -2738,15 +3921,23 @@
         <v>2.4246596338413204</v>
       </c>
       <c r="C142">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.3999999999999919</v>
       </c>
       <c r="D142">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4659633841328521E-2</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E142" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0274847433887064E-2</v>
+      </c>
+      <c r="F142" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0274847433886918E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2.4099999999999917E-2</v>
       </c>
@@ -2754,15 +3945,23 @@
         <v>2.4347595488791347</v>
       </c>
       <c r="C143">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4099999999999917</v>
       </c>
       <c r="D143">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4759548879143001E-2</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E143" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0273671734084297E-2</v>
+      </c>
+      <c r="F143" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0273671734084267E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2.4199999999999916E-2</v>
       </c>
@@ -2770,15 +3969,23 @@
         <v>2.4448594615720363</v>
       </c>
       <c r="C144">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4199999999999915</v>
       </c>
       <c r="D144">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4859461572044772E-2</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E144" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0272504781836736E-2</v>
+      </c>
+      <c r="F144" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0272504781836719E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2.4299999999999915E-2</v>
       </c>
@@ -2786,15 +3993,23 @@
         <v>2.4549593754373453</v>
       </c>
       <c r="C145">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4299999999999917</v>
       </c>
       <c r="D145">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.4959375437353604E-2</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E145" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0271347916606565E-2</v>
+      </c>
+      <c r="F145" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0271347916606456E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2.4399999999999915E-2</v>
       </c>
@@ -2802,15 +4017,23 @@
         <v>2.4650592916473903</v>
       </c>
       <c r="C146">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4399999999999915</v>
       </c>
       <c r="D146">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.505929164739884E-2</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E146" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0270201494835603E-2</v>
+      </c>
+      <c r="F146" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0270201494835625E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2.4499999999999914E-2</v>
       </c>
@@ -2818,15 +4041,23 @@
         <v>2.4751592055123965</v>
       </c>
       <c r="C147">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4499999999999913</v>
       </c>
       <c r="D147">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5159205512405247E-2</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E147" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0269063474451038E-2</v>
+      </c>
+      <c r="F147" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0269063474451157E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2.4599999999999914E-2</v>
       </c>
@@ -2834,15 +4065,23 @@
         <v>2.4852591193777691</v>
       </c>
       <c r="C148">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4599999999999915</v>
       </c>
       <c r="D148">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5259119377777584E-2</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E148" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0267934706413795E-2</v>
+      </c>
+      <c r="F148" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0267934706413687E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2.4699999999999913E-2</v>
       </c>
@@ -2850,15 +4089,23 @@
         <v>2.4953590320706374</v>
       </c>
       <c r="C149">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4699999999999913</v>
       </c>
       <c r="D149">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5359032070646048E-2</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E149" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0266814603500415E-2</v>
+      </c>
+      <c r="F149" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0266814603500461E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2.4799999999999912E-2</v>
       </c>
@@ -2866,15 +4113,23 @@
         <v>2.5054589447635478</v>
       </c>
       <c r="C150">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4799999999999911</v>
       </c>
       <c r="D150">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5458944763556701E-2</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E150" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0265703533692255E-2</v>
+      </c>
+      <c r="F150" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0265703533692255E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2.4899999999999912E-2</v>
       </c>
@@ -2882,15 +4137,23 @@
         <v>2.5155588598008709</v>
       </c>
       <c r="C151">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4899999999999913</v>
       </c>
       <c r="D151">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5558859800879574E-2</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E151" s="2">
+        <f t="shared" si="10"/>
+        <v>1.026460232967057E-2</v>
+      </c>
+      <c r="F151" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0264602329670547E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2.4999999999999911E-2</v>
       </c>
@@ -2898,15 +4161,23 @@
         <v>2.5256587736663909</v>
       </c>
       <c r="C152">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.4999999999999911</v>
       </c>
       <c r="D152">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5658773666399792E-2</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E152" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0263509466559887E-2</v>
+      </c>
+      <c r="F152" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0263509466559953E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2.5099999999999911E-2</v>
       </c>
@@ -2914,15 +4185,23 @@
         <v>2.5357586887041488</v>
       </c>
       <c r="C153">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5099999999999909</v>
       </c>
       <c r="D153">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5758688704157873E-2</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E153" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0262425778548891E-2</v>
+      </c>
+      <c r="F153" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0262425778548991E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2.519999999999991E-2</v>
       </c>
@@ -2930,15 +4209,23 @@
         <v>2.5458586025695076</v>
       </c>
       <c r="C154">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5199999999999911</v>
       </c>
       <c r="D154">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5858602569516442E-2</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E154" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0261350225998701E-2</v>
+      </c>
+      <c r="F154" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0261350225998625E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2.5299999999999909E-2</v>
       </c>
@@ -2946,15 +4233,23 @@
         <v>2.555958516434623</v>
       </c>
       <c r="C155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5299999999999909</v>
       </c>
       <c r="D155">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.5958516434632095E-2</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E155" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0260283175743947E-2</v>
+      </c>
+      <c r="F155" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0260283175743947E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2.5399999999999909E-2</v>
       </c>
@@ -2962,15 +4257,23 @@
         <v>2.5660584302997904</v>
       </c>
       <c r="C156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5399999999999907</v>
       </c>
       <c r="D156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6058430299799706E-2</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E156" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0259224527480192E-2</v>
+      </c>
+      <c r="F156" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0259224527480237E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2.5499999999999908E-2</v>
       </c>
@@ -2978,15 +4281,23 @@
         <v>2.5761583441650533</v>
       </c>
       <c r="C157">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5499999999999909</v>
       </c>
       <c r="D157">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6158344165062353E-2</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E157" s="2">
+        <f t="shared" si="10"/>
+        <v>1.025817418237749E-2</v>
+      </c>
+      <c r="F157" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0258174182377429E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2.5599999999999908E-2</v>
       </c>
@@ -2994,15 +4305,23 @@
         <v>2.5862582580303437</v>
       </c>
       <c r="C158">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5599999999999907</v>
       </c>
       <c r="D158">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6258258030352977E-2</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E158" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0257132043106609E-2</v>
+      </c>
+      <c r="F158" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0257132043106668E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2.5699999999999907E-2</v>
       </c>
@@ -3010,15 +4329,23 @@
         <v>2.5963581718957203</v>
       </c>
       <c r="C159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5699999999999905</v>
       </c>
       <c r="D159">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6358171895729754E-2</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E159" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0256098013902579E-2</v>
+      </c>
+      <c r="F159" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0256098013902665E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2.5799999999999906E-2</v>
       </c>
@@ -3026,15 +4353,23 @@
         <v>2.6064580869334195</v>
       </c>
       <c r="C160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5799999999999907</v>
       </c>
       <c r="D160">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.645808693342877E-2</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E160" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0255072454817438E-2</v>
+      </c>
+      <c r="F160" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0255072454817389E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2.5899999999999906E-2</v>
       </c>
@@ -3042,15 +4377,23 @@
         <v>2.6165580007984417</v>
       </c>
       <c r="C161">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5899999999999905</v>
       </c>
       <c r="D161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6558000798451165E-2</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E161" s="2">
+        <f t="shared" si="10"/>
+        <v>1.025405436233634E-2</v>
+      </c>
+      <c r="F161" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0254054362336394E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2.5999999999999905E-2</v>
       </c>
@@ -3058,15 +4401,23 @@
         <v>2.6266579134913703</v>
       </c>
       <c r="C162">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.5999999999999903</v>
       </c>
       <c r="D162">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6657913491380025E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E162" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0253043650530742E-2</v>
+      </c>
+      <c r="F162" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0253043650530817E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2.6099999999999905E-2</v>
       </c>
@@ -3074,15 +4425,23 @@
         <v>2.6367578285291122</v>
       </c>
       <c r="C163">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6099999999999905</v>
       </c>
       <c r="D163">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6757828529121674E-2</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E163" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0252041582039068E-2</v>
+      </c>
+      <c r="F163" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0252041582038993E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2.6199999999999904E-2</v>
       </c>
@@ -3090,15 +4449,23 @@
         <v>2.6468577423942841</v>
       </c>
       <c r="C164">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6199999999999903</v>
       </c>
       <c r="D164">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6857742394293727E-2</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E164" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0251046715379249E-2</v>
+      </c>
+      <c r="F164" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0251046715379323E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2.6299999999999903E-2</v>
       </c>
@@ -3106,15 +4473,23 @@
         <v>2.6569576562597854</v>
       </c>
       <c r="C165">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6299999999999901</v>
       </c>
       <c r="D165">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.6957656259795293E-2</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E165" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0250059414370814E-2</v>
+      </c>
+      <c r="F165" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0250059414370872E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2.6399999999999903E-2</v>
       </c>
@@ -3122,15 +4497,23 @@
         <v>2.6670575712973119</v>
       </c>
       <c r="C166">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6399999999999904</v>
       </c>
       <c r="D166">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7057571297321559E-2</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E166" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0249080036864328E-2</v>
+      </c>
+      <c r="F166" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0249080036864264E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2.6499999999999902E-2</v>
       </c>
@@ -3138,15 +4521,23 @@
         <v>2.6771574828178166</v>
       </c>
       <c r="C167">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6499999999999901</v>
       </c>
       <c r="D167">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7157482817826484E-2</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E167" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0248106723708177E-2</v>
+      </c>
+      <c r="F167" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0248106723708145E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2.6599999999999902E-2</v>
       </c>
@@ -3154,15 +4545,23 @@
         <v>2.6872573978556784</v>
       </c>
       <c r="C168">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6599999999999904</v>
       </c>
       <c r="D168">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7257397855688037E-2</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E168" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0247142051010677E-2</v>
+      </c>
+      <c r="F168" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0247142051010577E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2.6699999999999901E-2</v>
       </c>
@@ -3170,15 +4569,23 @@
         <v>2.6973573117206442</v>
       </c>
       <c r="C169">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6699999999999902</v>
       </c>
       <c r="D169">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7357311720654032E-2</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E169" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0246184165039075E-2</v>
+      </c>
+      <c r="F169" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0246184165039002E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2.67999999999999E-2</v>
       </c>
@@ -3186,15 +4593,23 @@
         <v>2.7074572255859133</v>
       </c>
       <c r="C170">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6799999999999899</v>
       </c>
       <c r="D170">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7457225585923339E-2</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E170" s="2">
+        <f t="shared" si="10"/>
+        <v>1.024523342758339E-2</v>
+      </c>
+      <c r="F170" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0245233427583374E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2.68999999999999E-2</v>
       </c>
@@ -3202,15 +4617,23 @@
         <v>2.7175571394514173</v>
       </c>
       <c r="C171">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.6899999999999902</v>
       </c>
       <c r="D171">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7557139451427126E-2</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E171" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0244289758894989E-2</v>
+      </c>
+      <c r="F171" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0244289758894879E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2.6999999999999899E-2</v>
       </c>
@@ -3218,15 +4641,23 @@
         <v>2.7276570544890482</v>
       </c>
       <c r="C172">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.69999999999999</v>
       </c>
       <c r="D172">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7657054489058197E-2</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E172" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0243353514465996E-2</v>
+      </c>
+      <c r="F172" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0243353514466038E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2.7099999999999898E-2</v>
       </c>
@@ -3234,15 +4665,23 @@
         <v>2.7377569695262847</v>
       </c>
       <c r="C173">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7099999999999898</v>
       </c>
       <c r="D173">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7756969526294917E-2</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E173" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0242424179444678E-2</v>
+      </c>
+      <c r="F173" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0242424179444657E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2.7199999999999898E-2</v>
       </c>
@@ -3250,15 +4689,23 @@
         <v>2.7478568810468516</v>
       </c>
       <c r="C174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.71999999999999</v>
       </c>
       <c r="D174">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.785688104686157E-2</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E174" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0241500384875743E-2</v>
+      </c>
+      <c r="F174" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0241500384875615E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2.7299999999999897E-2</v>
       </c>
@@ -3266,15 +4713,23 @@
         <v>2.7579567972570049</v>
       </c>
       <c r="C175">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7299999999999898</v>
       </c>
       <c r="D175">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.7956797257015165E-2</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E175" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0240585075829738E-2</v>
+      </c>
+      <c r="F175" s="2">
+        <f t="shared" si="11"/>
+        <v>1.024058507582977E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2.7399999999999897E-2</v>
       </c>
@@ -3282,15 +4737,23 @@
         <v>2.7680567111224756</v>
       </c>
       <c r="C176">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7399999999999896</v>
       </c>
       <c r="D176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8056711122486089E-2</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E176" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0239675592148145E-2</v>
+      </c>
+      <c r="F176" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0239675592148247E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2.7499999999999896E-2</v>
       </c>
@@ -3298,15 +4761,23 @@
         <v>2.7781566238149509</v>
       </c>
       <c r="C177">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7499999999999898</v>
       </c>
       <c r="D177">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.815662381496109E-2</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E177" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0238772296349551E-2</v>
+      </c>
+      <c r="F177" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0238772296349525E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2.7599999999999895E-2</v>
       </c>
@@ -3314,15 +4785,23 @@
         <v>2.7882565376802586</v>
       </c>
       <c r="C178">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7599999999999896</v>
       </c>
       <c r="D178">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8256537680269034E-2</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E178" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0237875971112058E-2</v>
+      </c>
+      <c r="F178" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0237875971112007E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2.7699999999999895E-2</v>
       </c>
@@ -3330,15 +4809,23 @@
         <v>2.7983564550627795</v>
       </c>
       <c r="C179">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7699999999999894</v>
       </c>
       <c r="D179">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8356455062790165E-2</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E179" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0236987387288883E-2</v>
+      </c>
+      <c r="F179" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0236987387288907E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2.7799999999999894E-2</v>
       </c>
@@ -3346,15 +4833,23 @@
         <v>2.808456367755892</v>
       </c>
       <c r="C180">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7799999999999896</v>
       </c>
       <c r="D180">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8456367755902434E-2</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E180" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0236103509317461E-2</v>
+      </c>
+      <c r="F180" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0236103509317461E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2.7899999999999894E-2</v>
       </c>
@@ -3362,15 +4857,23 @@
         <v>2.8185562804486612</v>
       </c>
       <c r="C181">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7899999999999894</v>
       </c>
       <c r="D181">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8556280448671867E-2</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E181" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0235225967265987E-2</v>
+      </c>
+      <c r="F181" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0235225967265942E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2.7999999999999893E-2</v>
       </c>
@@ -3378,15 +4881,23 @@
         <v>2.8286561943139361</v>
       </c>
       <c r="C182">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.7999999999999892</v>
       </c>
       <c r="D182">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8656194313946948E-2</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E182" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0234355112123859E-2</v>
+      </c>
+      <c r="F182" s="2">
+        <f t="shared" si="11"/>
+        <v>1.023435511212395E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2.8099999999999892E-2</v>
       </c>
@@ -3394,15 +4905,23 @@
         <v>2.8387561093514084</v>
       </c>
       <c r="C183">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8099999999999894</v>
       </c>
       <c r="D183">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8756109351419035E-2</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E183" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0233490872391199E-2</v>
+      </c>
+      <c r="F183" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0233490872391154E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2.8199999999999892E-2</v>
       </c>
@@ -3410,15 +4929,23 @@
         <v>2.8488560232169022</v>
       </c>
       <c r="C184">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8199999999999892</v>
       </c>
       <c r="D184">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8856023216913051E-2</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E184" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0232632346423137E-2</v>
+      </c>
+      <c r="F184" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0232632346423107E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2.8299999999999891E-2</v>
       </c>
@@ -3426,15 +4953,23 @@
         <v>2.8589559382545189</v>
       </c>
       <c r="C185">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.829999999999989</v>
       </c>
       <c r="D185">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.8955938254529912E-2</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E185" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0231780301954077E-2</v>
+      </c>
+      <c r="F185" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0231780301954072E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2.8399999999999891E-2</v>
       </c>
@@ -3442,15 +4977,23 @@
         <v>2.8690558521198732</v>
       </c>
       <c r="C186">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8399999999999892</v>
       </c>
       <c r="D186">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.905585211988404E-2</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E186" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0230933845029646E-2</v>
+      </c>
+      <c r="F186" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0230933845029631E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2.849999999999989E-2</v>
       </c>
@@ -3458,15 +5001,23 @@
         <v>2.8791557659850113</v>
       </c>
       <c r="C187">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.849999999999989</v>
       </c>
       <c r="D187">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9155765985022342E-2</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E187" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0230093328078088E-2</v>
+      </c>
+      <c r="F187" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0230093328078053E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2.8599999999999889E-2</v>
       </c>
@@ -3474,15 +5025,23 @@
         <v>2.8892556798505429</v>
       </c>
       <c r="C188">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8599999999999888</v>
       </c>
       <c r="D188">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9255679850554106E-2</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E188" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0229258689004895E-2</v>
+      </c>
+      <c r="F188" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0229258689004973E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2.8699999999999889E-2</v>
       </c>
@@ -3490,15 +5049,23 @@
         <v>2.8993555937153226</v>
       </c>
       <c r="C189">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.869999999999989</v>
       </c>
       <c r="D189">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9355593715333583E-2</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E189" s="2">
+        <f t="shared" si="10"/>
+        <v>1.022842986597002E-2</v>
+      </c>
+      <c r="F189" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0228429865969928E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2.8799999999999888E-2</v>
       </c>
@@ -3506,15 +5073,23 @@
         <v>2.9094555064081513</v>
       </c>
       <c r="C190">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8799999999999888</v>
       </c>
       <c r="D190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9455506408162524E-2</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E190" s="2">
+        <f t="shared" si="10"/>
+        <v>1.022760639172309E-2</v>
+      </c>
+      <c r="F190" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0227606391723138E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2.8899999999999888E-2</v>
       </c>
@@ -3522,15 +5097,23 @@
         <v>2.9195554191012087</v>
       </c>
       <c r="C191">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8899999999999886</v>
       </c>
       <c r="D191">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9555419101220171E-2</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E191" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0226788616339109E-2</v>
+      </c>
+      <c r="F191" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0226788616339199E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2.8999999999999887E-2</v>
       </c>
@@ -3538,15 +5121,23 @@
         <v>2.9296553341390168</v>
       </c>
       <c r="C192">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.8999999999999888</v>
       </c>
       <c r="D192">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9655334139027989E-2</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E192" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0225977289320112E-2</v>
+      </c>
+      <c r="F192" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0225977289320036E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2.9099999999999886E-2</v>
       </c>
@@ -3554,15 +5145,23 @@
         <v>2.9397552491766312</v>
       </c>
       <c r="C193">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.9099999999999886</v>
       </c>
       <c r="D193">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9755249176642629E-2</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E193" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0225171538365186E-2</v>
+      </c>
+      <c r="F193" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0225171538365205E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2.9199999999999886E-2</v>
       </c>
@@ -3570,15 +5169,23 @@
         <v>2.9498551642143473</v>
       </c>
       <c r="C194">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.9199999999999884</v>
       </c>
       <c r="D194">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2.9855164214358965E-2</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E194" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0224371306287347E-2</v>
+      </c>
+      <c r="F194" s="2">
+        <f t="shared" si="11"/>
+        <v>1.0224371306287358E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2.9299999999999885E-2</v>
       </c>
@@ -3586,15 +5193,23 @@
         <v>2.9599550769069745</v>
       </c>
       <c r="C195">
-        <f t="shared" ref="C195:C202" si="6">A195*100</f>
+        <f t="shared" ref="C195:C202" si="12">A195*100</f>
         <v>2.9299999999999886</v>
       </c>
       <c r="D195">
-        <f t="shared" ref="D195:D202" si="7">B195-C195</f>
+        <f t="shared" ref="D195:D202" si="13">B195-C195</f>
         <v>2.9955076906985845E-2</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E195" s="2">
+        <f t="shared" ref="E195:E202" si="14">(B195/100-A195)/A195</f>
+        <v>1.0223575736172703E-2</v>
+      </c>
+      <c r="F195" s="2">
+        <f t="shared" ref="F195:F202" si="15">(B195-C195)/C195</f>
+        <v>1.0223575736172682E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2.9399999999999885E-2</v>
       </c>
@@ -3602,15 +5217,23 @@
         <v>2.9700549907724709</v>
       </c>
       <c r="C196">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.9399999999999884</v>
       </c>
       <c r="D196">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0054990772482526E-2</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E196" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0222785977034837E-2</v>
+      </c>
+      <c r="F196" s="2">
+        <f t="shared" si="15"/>
+        <v>1.0222785977034913E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2.9499999999999884E-2</v>
       </c>
@@ -3618,15 +5241,23 @@
         <v>2.9801549058100218</v>
       </c>
       <c r="C197">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.9499999999999882</v>
       </c>
       <c r="D197">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0154905810033661E-2</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E197" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0222001969502929E-2</v>
+      </c>
+      <c r="F197" s="2">
+        <f t="shared" si="15"/>
+        <v>1.0222001969502978E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2.9599999999999883E-2</v>
       </c>
@@ -3634,15 +5265,23 @@
         <v>2.9902548196751098</v>
       </c>
       <c r="C198">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.9599999999999884</v>
       </c>
       <c r="D198">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0254819675121336E-2</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E198" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0221222863216788E-2</v>
+      </c>
+      <c r="F198" s="2">
+        <f t="shared" si="15"/>
+        <v>1.0221222863216707E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2.9699999999999883E-2</v>
       </c>
@@ -3650,15 +5289,23 @@
         <v>3.0003547335403797</v>
       </c>
       <c r="C199">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.9699999999999882</v>
       </c>
       <c r="D199">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0354733540391532E-2</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E199" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0220449003498834E-2</v>
+      </c>
+      <c r="F199" s="2">
+        <f t="shared" si="15"/>
+        <v>1.0220449003498873E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2.9799999999999882E-2</v>
       </c>
@@ -3666,15 +5313,23 @@
         <v>3.0104546474058815</v>
       </c>
       <c r="C200">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.979999999999988</v>
       </c>
       <c r="D200">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0454647405893542E-2</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E200" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0219680337548153E-2</v>
+      </c>
+      <c r="F200" s="2">
+        <f t="shared" si="15"/>
+        <v>1.021968033754821E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2.9899999999999882E-2</v>
       </c>
@@ -3682,15 +5337,23 @@
         <v>3.0205545624433214</v>
       </c>
       <c r="C201">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.9899999999999882</v>
       </c>
       <c r="D201">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0554562443333211E-2</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E201" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0218917205128209E-2</v>
+      </c>
+      <c r="F201" s="2">
+        <f t="shared" si="15"/>
+        <v>1.0218917205128204E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2.9999999999999881E-2</v>
       </c>
@@ -3698,12 +5361,20 @@
         <v>3.0306544751361613</v>
       </c>
       <c r="C202">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>2.999999999999988</v>
       </c>
       <c r="D202">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3.0654475136173254E-2</v>
+      </c>
+      <c r="E202" s="2">
+        <f t="shared" si="14"/>
+        <v>1.0218158378724444E-2</v>
+      </c>
+      <c r="F202" s="2">
+        <f t="shared" si="15"/>
+        <v>1.021815837872446E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Homework2/my-simulation/question6.xlsx
+++ b/Homework2/my-simulation/question6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD30548-6F14-4F70-A53C-7A18DA85D4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFAEF0F-E7F3-4927-AA8C-E9B69E4E74E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E80FAFA-0C40-4CBD-8A86-3F1424DEA9C9}"/>
   </bookViews>
@@ -509,15 +509,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <f>B2-C2</f>
+        <f>ABS(B2-C2)</f>
         <v>1.0671669256573146E-2</v>
       </c>
       <c r="E2" s="2">
-        <f>(B2/100-A2)/A2</f>
+        <f>ABS(B2/100-A2)/A2</f>
         <v>1.0671669256573195E-2</v>
       </c>
       <c r="F2" s="2">
-        <f>(B2-C2)/C2</f>
+        <f>ABS(B2-C2)/C2</f>
         <v>1.0671669256573146E-2</v>
       </c>
       <c r="G2" t="s">
@@ -540,15 +540,15 @@
         <v>1.01</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D66" si="1">B3-C3</f>
+        <f t="shared" ref="D3:D66" si="1">ABS(B3-C3)</f>
         <v>1.0771583290991149E-2</v>
       </c>
       <c r="E3" s="2">
-        <f t="shared" ref="E3:E66" si="2">(B3/100-A3)/A3</f>
+        <f t="shared" ref="E3:E66" si="2">ABS(B3/100-A3)/A3</f>
         <v>1.0664933951476482E-2</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F66" si="3">(B3-C3)/C3</f>
+        <f t="shared" ref="F3:F66" si="3">ABS(B3-C3)/C3</f>
         <v>1.0664933951476385E-2</v>
       </c>
       <c r="G3" t="s">
@@ -2125,15 +2125,15 @@
         <v>1.6499999999999964</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D130" si="5">B67-C67</f>
+        <f t="shared" ref="D67:D130" si="5">ABS(B67-C67)</f>
         <v>1.7166078705646681E-2</v>
       </c>
       <c r="E67" s="2">
-        <f t="shared" ref="E67:E130" si="6">(B67/100-A67)/A67</f>
+        <f t="shared" ref="E67:E130" si="6">ABS(B67/100-A67)/A67</f>
         <v>1.0403684064028458E-2</v>
       </c>
       <c r="F67" s="2">
-        <f t="shared" ref="F67:F130" si="7">(B67-C67)/C67</f>
+        <f t="shared" ref="F67:F130" si="7">ABS(B67-C67)/C67</f>
         <v>1.0403684064028315E-2</v>
       </c>
     </row>
@@ -3661,15 +3661,15 @@
         <v>2.2899999999999925</v>
       </c>
       <c r="D131">
-        <f t="shared" ref="D131:D194" si="9">B131-C131</f>
+        <f t="shared" ref="D131:D194" si="9">ABS(B131-C131)</f>
         <v>2.3560578978897073E-2</v>
       </c>
       <c r="E131" s="2">
-        <f t="shared" ref="E131:E194" si="10">(B131/100-A131)/A131</f>
+        <f t="shared" ref="E131:E194" si="10">ABS(B131/100-A131)/A131</f>
         <v>1.0288462436199606E-2</v>
       </c>
       <c r="F131" s="2">
-        <f t="shared" ref="F131:F194" si="11">(B131-C131)/C131</f>
+        <f t="shared" ref="F131:F194" si="11">ABS(B131-C131)/C131</f>
         <v>1.0288462436199628E-2</v>
       </c>
     </row>
@@ -5197,15 +5197,15 @@
         <v>2.9299999999999886</v>
       </c>
       <c r="D195">
-        <f t="shared" ref="D195:D202" si="13">B195-C195</f>
+        <f t="shared" ref="D195:D202" si="13">ABS(B195-C195)</f>
         <v>2.9955076906985845E-2</v>
       </c>
       <c r="E195" s="2">
-        <f t="shared" ref="E195:E202" si="14">(B195/100-A195)/A195</f>
+        <f t="shared" ref="E195:E202" si="14">ABS(B195/100-A195)/A195</f>
         <v>1.0223575736172703E-2</v>
       </c>
       <c r="F195" s="2">
-        <f t="shared" ref="F195:F202" si="15">(B195-C195)/C195</f>
+        <f t="shared" ref="F195:F202" si="15">ABS(B195-C195)/C195</f>
         <v>1.0223575736172682E-2</v>
       </c>
     </row>
